--- a/V5.0_双人执行工作区/A_数据平台/03_Smartbi证据/A03/SMARTBI_IMPORT_RECONCILIATION_V50.xlsx
+++ b/V5.0_双人执行工作区/A_数据平台/03_Smartbi证据/A03/SMARTBI_IMPORT_RECONCILIATION_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入对账" sheetId="1" r:id="Raeeae998109546d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入对账" sheetId="1" r:id="Rdd8cd98fd0cb4d73"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -309,7 +309,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2" ht="36" customHeight="1">
+    <x:row r="2" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1</x:t>
@@ -346,17 +346,17 @@
       <x:c r="H2" s="1" t="str">
         <x:v>一致（截图：逐表截图/01_dim_country.png）</x:v>
       </x:c>
-      <x:c r="I2" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J2" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I2" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K2" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2</x:t>
@@ -393,17 +393,17 @@
       <x:c r="H3" s="1" t="str">
         <x:v>一致（截图：逐表截图/02_dim_date.png）</x:v>
       </x:c>
-      <x:c r="I3" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J3" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I3" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J3" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K3" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">3</x:t>
@@ -440,17 +440,17 @@
       <x:c r="H4" s="1" t="str">
         <x:v>一致（截图：逐表截图/03_dim_year.png）</x:v>
       </x:c>
-      <x:c r="I4" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J4" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I4" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J4" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K4" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">4</x:t>
@@ -487,17 +487,17 @@
       <x:c r="H5" s="1" t="str">
         <x:v>一致（截图：逐表截图/04_dim_company.png）</x:v>
       </x:c>
-      <x:c r="I5" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J5" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I5" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J5" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K5" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">5</x:t>
@@ -534,17 +534,17 @@
       <x:c r="H6" s="1" t="str">
         <x:v>一致（截图：逐表截图/05_dim_asset.png）</x:v>
       </x:c>
-      <x:c r="I6" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J6" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I6" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J6" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K6" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">6</x:t>
@@ -581,17 +581,17 @@
       <x:c r="H7" s="1" t="str">
         <x:v>一致（截图：逐表截图/06_dim_event.png）</x:v>
       </x:c>
-      <x:c r="I7" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J7" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I7" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J7" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K7" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">7</x:t>
@@ -628,17 +628,17 @@
       <x:c r="H8" s="1" t="str">
         <x:v>一致（截图：逐表截图/07_country_exposure.png）</x:v>
       </x:c>
-      <x:c r="I8" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J8" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I8" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K8" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">8</x:t>
@@ -675,17 +675,17 @@
       <x:c r="H9" s="1" t="str">
         <x:v>一致（截图：逐表截图/08_country_monthly_risk.png）</x:v>
       </x:c>
-      <x:c r="I9" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J9" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I9" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K9" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A10" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">9</x:t>
@@ -722,17 +722,17 @@
       <x:c r="H10" s="1" t="str">
         <x:v>一致（截图：逐表截图/09_country_policy_year.png）</x:v>
       </x:c>
-      <x:c r="I10" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J10" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I10" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K10" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A11" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">10</x:t>
@@ -769,17 +769,17 @@
       <x:c r="H11" s="1" t="str">
         <x:v>一致（截图：逐表截图/10_country_event.png）</x:v>
       </x:c>
-      <x:c r="I11" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J11" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I11" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K11" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">11</x:t>
@@ -816,17 +816,17 @@
       <x:c r="H12" s="1" t="str">
         <x:v>一致（截图：逐表截图/11_global_cycle_month.png）</x:v>
       </x:c>
-      <x:c r="I12" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J12" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I12" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K12" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">12</x:t>
@@ -863,17 +863,17 @@
       <x:c r="H13" s="1" t="str">
         <x:v>一致（截图：逐表截图/12_historical_crisis_event.png）</x:v>
       </x:c>
-      <x:c r="I13" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J13" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I13" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K13" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">13</x:t>
@@ -910,17 +910,17 @@
       <x:c r="H14" s="1" t="str">
         <x:v>一致（截图：逐表截图/13_company_overseas_exposure.png）</x:v>
       </x:c>
-      <x:c r="I14" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J14" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I14" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K14" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">14</x:t>
@@ -957,17 +957,17 @@
       <x:c r="H15" s="1" t="str">
         <x:v>一致（截图：逐表截图/14_bridge_company_geography.png）</x:v>
       </x:c>
-      <x:c r="I15" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J15" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I15" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K15" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">15</x:t>
@@ -1004,17 +1004,17 @@
       <x:c r="H16" s="1" t="str">
         <x:v>一致（截图：逐表截图/15_asset_monthly_return.png）</x:v>
       </x:c>
-      <x:c r="I16" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J16" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I16" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K16" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">16</x:t>
@@ -1051,17 +1051,17 @@
       <x:c r="H17" s="1" t="str">
         <x:v>一致（截图：逐表截图/16_portfolio_scenario.png）</x:v>
       </x:c>
-      <x:c r="I17" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J17" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I17" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K17" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">17</x:t>
@@ -1098,17 +1098,17 @@
       <x:c r="H18" s="1" t="str">
         <x:v>一致（截图：逐表截图/17_case_evidence.png）</x:v>
       </x:c>
-      <x:c r="I18" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J18" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I18" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K18" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">18</x:t>
@@ -1145,17 +1145,17 @@
       <x:c r="H19" s="1" t="str">
         <x:v>一致（截图：逐表截图/18_source_registry.png）</x:v>
       </x:c>
-      <x:c r="I19" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J19" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I19" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K19" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">19</x:t>
@@ -1192,17 +1192,17 @@
       <x:c r="H20" s="1" t="str">
         <x:v>一致（截图：逐表截图/19_MVP_country_latest.png）</x:v>
       </x:c>
-      <x:c r="I20" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J20" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I20" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K20" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">20</x:t>
@@ -1239,17 +1239,17 @@
       <x:c r="H21" s="1" t="str">
         <x:v>一致（截图：逐表截图/20_MVP_company_data_status.png）</x:v>
       </x:c>
-      <x:c r="I21" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J21" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I21" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J21" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K21" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="36" customHeight="1">
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -1286,14 +1286,14 @@
       <x:c r="H22" s="1" t="str">
         <x:v>一致（截图：逐表截图/21_MVP_cycle_state.png）</x:v>
       </x:c>
-      <x:c r="I22" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
-      </x:c>
-      <x:c r="J22" s="1" t="str">
-        <x:v>0（源端审计+A报告；平台未查询）</x:v>
+      <x:c r="I22" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J22" s="1" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K22" s="1" t="str">
-        <x:v>BLOCKED（行数已证；主键/类型缺平台证据）</x:v>
+        <x:v>BLOCKED（主键平台实测PASS；类型/资源锁待核）。证据：A03_PK_AUDIT_20260904/README.md</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="36" customHeight="1">
